--- a/technology_surveys/028_twitch_survey--technology_surveys.xlsx
+++ b/technology_surveys/028_twitch_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fortnite',_'label':_'fortnite'}</t>
+          <t>fortnite</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Fortnite', 'label': 'Fortnite'}</t>
+          <t>Fortnite</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'apex_legends',_'label':_'apex_legends'}</t>
+          <t>apex_legends</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Apex Legends', 'label': 'Apex Legends'}</t>
+          <t>Apex Legends</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'league_of_legends',_'label':_'league_of_legends'}</t>
+          <t>league_of_legends</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'League of Legends', 'label': 'League of Legends'}</t>
+          <t>League of Legends</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fortnite',_'label':_'fortnite'}</t>
+          <t>fortnite</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Fortnite', 'label': 'Fortnite'}</t>
+          <t>Fortnite</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'apex_legends',_'label':_'apex_legends'}</t>
+          <t>apex_legends</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Apex Legends', 'label': 'Apex Legends'}</t>
+          <t>Apex Legends</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'league_of_legends',_'label':_'league_of_legends'}</t>
+          <t>league_of_legends</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'League of Legends', 'label': 'League of Legends'}</t>
+          <t>League of Legends</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'multiplayer',_'label':_'multiplayer'}</t>
+          <t>multiplayer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Multiplayer', 'label': 'Multiplayer'}</t>
+          <t>Multiplayer</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'singleplayer',_'label':_'singleplayer'}</t>
+          <t>singleplayer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Singleplayer', 'label': 'Singleplayer'}</t>
+          <t>Singleplayer</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'co-op',_'label':_'co-op'}</t>
+          <t>co-op</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Co-op', 'label': 'Co-op'}</t>
+          <t>Co-op</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'often',_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Often', 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sometimes',_'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sometimes', 'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'often',_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Often', 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sometimes',_'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sometimes', 'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'1-2',_'label':_'1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '1-2', 'label': '1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'3-5',_'label':_'3-5'}</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '3-5', 'label': '3-5'}</t>
+          <t>3-5</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'6-10',_'label':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '6-10', 'label': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'more_than_10',_'label':_'more_than_10'}</t>
+          <t>more_than_10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'More than 10', 'label': 'More than 10'}</t>
+          <t>More than 10</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'gaming',_'label':_'gaming'}</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Gaming', 'label': 'Gaming'}</t>
+          <t>Gaming</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'music',_'label':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Music', 'label': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'talk',_'label':_'talk'}</t>
+          <t>talk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Talk', 'label': 'Talk'}</t>
+          <t>Talk</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'art',_'label':_'art'}</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Art', 'label': 'Art'}</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'live',_'label':_'live'}</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Live', 'label': 'Live'}</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'vod',_'label':_'vod'}</t>
+          <t>vod</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'VOD', 'label': 'VOD'}</t>
+          <t>VOD</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'clips',_'label':_'clips'}</t>
+          <t>clips</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Clips', 'label': 'Clips'}</t>
+          <t>Clips</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
